--- a/DateBase/orders/Dang Nguyen 195_2026-3-5.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-3-5.xlsx
@@ -619,6 +619,9 @@
       <c r="G2" t="str">
         <v>029201420301020505050202070</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
